--- a/data/processed/GCD/tables/hBN_GCD_fit_summary_refit_auxiliary.xlsx
+++ b/data/processed/GCD/tables/hBN_GCD_fit_summary_refit_auxiliary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF6"/>
+  <dimension ref="A1:AO6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,25 +554,70 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
+          <t>window_selection_method</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>flatness_score</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>mean_stability_cost</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>slope_cv</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>slope_magnitude_fraction</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>linearity_rmse_fraction</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>smoothed_R2</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>window_voltage_span_fraction</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>window_point_fraction</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
           <t>selected_t_start_s</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>selected_t_end_s</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>selected_duration_s</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>N_selected</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>deltaV_IR_mV_from_bestRs</t>
         </is>
@@ -583,16 +628,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2808998495376823</v>
+        <v>0.2537316398228566</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2273035985902431</v>
+        <v>0.2177949015737403</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1728981157928321</v>
+        <v>0.1855998158946897</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2788139568476453</v>
+        <v>0.251491677559279</v>
       </c>
       <c r="F2" t="n">
         <v>0.009867003129131019</v>
@@ -607,16 +652,16 @@
         <v>0.009867003129131019</v>
       </c>
       <c r="J2" t="n">
-        <v>82.08268396494205</v>
+        <v>99.0876457235766</v>
       </c>
       <c r="K2" t="n">
-        <v>82.18846672879607</v>
+        <v>99.12647789014086</v>
       </c>
       <c r="L2" t="n">
-        <v>80.31299522823559</v>
+        <v>98.6000265889823</v>
       </c>
       <c r="M2" t="n">
-        <v>84.47052639463416</v>
+        <v>99.65238835783501</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -643,36 +688,65 @@
         <v>9</v>
       </c>
       <c r="V2" t="n">
-        <v>6.912834321554545e-05</v>
+        <v>2.763412452558101e-06</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.01218283749623861</v>
+        <v>-0.01009207548224211</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2710328464085513</v>
+        <v>0.2438646366937256</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.9378032927535296</v>
+        <v>0.9937413253113716</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.3156176122607104</v>
+        <v>0.2470939836204819</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1481240682800154</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.020404070033699</v>
+        <v>0.1716943911215906</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>flattest_linear_post_ir_window</t>
+        </is>
       </c>
       <c r="AC2" t="n">
-        <v>10.1904039400397</v>
+        <v>0.4090083896037332</v>
       </c>
       <c r="AD2" t="n">
-        <v>9.169999870006</v>
+        <v>0.005105930780724575</v>
       </c>
       <c r="AE2" t="n">
-        <v>918</v>
+        <v>0.2038099953039345</v>
       </c>
       <c r="AF2" t="n">
+        <v>0.8587077742785689</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.02204950757403997</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.9937397197821359</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1800656686984466</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.6645101663585952</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>2.480403420049704</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>9.660403930000101</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>7.180000509950396</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>719</v>
+      </c>
+      <c r="AO2" t="n">
         <v>9.867003129131019</v>
       </c>
     </row>
@@ -681,16 +755,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2837189520967451</v>
+        <v>0.2618697187305725</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2228335040859368</v>
+        <v>0.2272136017138796</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1744678186185399</v>
+        <v>0.1909342262815798</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2812268620590055</v>
+        <v>0.2591578101708976</v>
       </c>
       <c r="F3" t="n">
         <v>0.009732716467688456</v>
@@ -705,16 +779,16 @@
         <v>0.009732716467688456</v>
       </c>
       <c r="J3" t="n">
-        <v>80.75702396739435</v>
+        <v>90.02908328210498</v>
       </c>
       <c r="K3" t="n">
-        <v>80.74079055931318</v>
+        <v>90.01799915214005</v>
       </c>
       <c r="L3" t="n">
-        <v>80.20990188044964</v>
+        <v>89.9074379826454</v>
       </c>
       <c r="M3" t="n">
-        <v>81.19577048147131</v>
+        <v>90.13615425000829</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -741,36 +815,65 @@
         <v>9</v>
       </c>
       <c r="V3" t="n">
-        <v>2.53243656432116e-05</v>
+        <v>7.395362157482108e-07</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.02476564763960966</v>
+        <v>-0.022215043484704</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2642535191613682</v>
+        <v>0.2424042857951956</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.9762301186337634</v>
+        <v>0.9983594015091282</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.29383878138548</v>
+        <v>0.2430605323091881</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1370719402663953</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.6164643500233069</v>
+        <v>0.1701718812136738</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>flattest_linear_post_ir_window</t>
+        </is>
       </c>
       <c r="AC3" t="n">
-        <v>5.126464340020903</v>
+        <v>0.2976232637509973</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.509999989997596</v>
+        <v>0.003125814721382655</v>
       </c>
       <c r="AE3" t="n">
-        <v>4511</v>
+        <v>0.09980240121056655</v>
       </c>
       <c r="AF3" t="n">
+        <v>0.9144866377887063</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.01179772026130688</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.9983595664406294</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1859797660658249</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.6185489902767389</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.294464180013208</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>4.601464139996096</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>3.306999959982889</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>3308</v>
+      </c>
+      <c r="AO3" t="n">
         <v>19.46543293537691</v>
       </c>
     </row>
@@ -779,16 +882,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2888111214176615</v>
+        <v>0.2704394929563628</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2304765973327792</v>
+        <v>0.2334202096327406</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1789813004228951</v>
+        <v>0.2016192663000049</v>
       </c>
       <c r="E4" t="n">
-        <v>0.285491288027338</v>
+        <v>0.2684717613610291</v>
       </c>
       <c r="F4" t="n">
         <v>0.009627444607500105</v>
@@ -803,16 +906,16 @@
         <v>0.009627444607500105</v>
       </c>
       <c r="J4" t="n">
-        <v>76.6425806985272</v>
+        <v>82.62651540927513</v>
       </c>
       <c r="K4" t="n">
-        <v>76.63493837340822</v>
+        <v>82.61991512795704</v>
       </c>
       <c r="L4" t="n">
-        <v>76.17881501183567</v>
+        <v>82.5122170999024</v>
       </c>
       <c r="M4" t="n">
-        <v>77.05125729670256</v>
+        <v>82.72682779643704</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -839,36 +942,65 @@
         <v>9</v>
       </c>
       <c r="V4" t="n">
-        <v>1.157318684391561e-05</v>
+        <v>3.828823840697951e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.03914273205126624</v>
+        <v>-0.03630795738075188</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2599287875951612</v>
+        <v>0.2415571591338625</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.9894381131399591</v>
+        <v>0.9991328965462332</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2762566247911574</v>
+        <v>0.2403482630997007</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1285968012516616</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.4754521000440088</v>
+        <v>0.1686803802188653</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>flattest_linear_post_ir_window</t>
+        </is>
       </c>
       <c r="AC4" t="n">
-        <v>3.388452050044009</v>
+        <v>0.2681048894817717</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.91299995</v>
+        <v>0.003212541545538136</v>
       </c>
       <c r="AE4" t="n">
-        <v>2914</v>
+        <v>0.06917872854335212</v>
       </c>
       <c r="AF4" t="n">
+        <v>0.9354012634119526</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.008633366710490951</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.9991330056590396</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.1941432169236362</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.5722444317532839</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.8774522900350088</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>2.880452080048002</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>2.002999790012993</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2004</v>
+      </c>
+      <c r="AO4" t="n">
         <v>28.88233382250031</v>
       </c>
     </row>
@@ -877,16 +1009,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2940145966772055</v>
+        <v>0.2578444668184073</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2326471314724497</v>
+        <v>0.2250812286125191</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1817620742310081</v>
+        <v>0.1969902141635942</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2902227436913513</v>
+        <v>0.2560473574389029</v>
       </c>
       <c r="F5" t="n">
         <v>0.009465826381994863</v>
@@ -901,16 +1033,16 @@
         <v>0.009465826381994863</v>
       </c>
       <c r="J5" t="n">
-        <v>71.8581587139351</v>
+        <v>70.89006794626557</v>
       </c>
       <c r="K5" t="n">
-        <v>71.88112973041225</v>
+        <v>70.88641253948954</v>
       </c>
       <c r="L5" t="n">
-        <v>71.41374029367795</v>
+        <v>70.75556429483144</v>
       </c>
       <c r="M5" t="n">
-        <v>72.27242579298996</v>
+        <v>71.08057868838678</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -937,36 +1069,65 @@
         <v>9</v>
       </c>
       <c r="V5" t="n">
-        <v>1.282379382344066e-05</v>
+        <v>3.020408842003765e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.05566521702739232</v>
+        <v>-0.05642539379468484</v>
       </c>
       <c r="X5" t="n">
-        <v>0.256151291149226</v>
+        <v>0.2199811612904279</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.9888430252200385</v>
+        <v>0.9990851477962761</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.2607275231705207</v>
+        <v>0.2184262390941888</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1213547092831069</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.410445009940986</v>
+        <v>0.1557072569013445</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>flattest_linear_post_ir_window</t>
+        </is>
       </c>
       <c r="AC5" t="n">
-        <v>2.507445010007985</v>
+        <v>0.2966933910250072</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.097000000066999</v>
+        <v>0.006238902074437486</v>
       </c>
       <c r="AE5" t="n">
-        <v>2098</v>
+        <v>0.08745606385157213</v>
       </c>
       <c r="AF5" t="n">
+        <v>0.9711828412875031</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.008761856841496954</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.9990853061663325</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.180003489758079</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.4335147744945568</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.111445009942003</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2.225445410004</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.114000400061997</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1115</v>
+      </c>
+      <c r="AO5" t="n">
         <v>37.86330552797945</v>
       </c>
     </row>
@@ -975,16 +1136,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2978504356018702</v>
+        <v>0.2578480005956012</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2378566748193664</v>
+        <v>0.2287151148614127</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1864920872476206</v>
+        <v>0.2019028414552028</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2948139771653032</v>
+        <v>0.2573337330206235</v>
       </c>
       <c r="F6" t="n">
         <v>0.009339393602113992</v>
@@ -999,16 +1160,16 @@
         <v>0.009339393602113992</v>
       </c>
       <c r="J6" t="n">
-        <v>66.63859685454328</v>
+        <v>61.27702420765139</v>
       </c>
       <c r="K6" t="n">
-        <v>66.61154707768503</v>
+        <v>61.25395957124961</v>
       </c>
       <c r="L6" t="n">
-        <v>65.89827369558307</v>
+        <v>60.92660592733132</v>
       </c>
       <c r="M6" t="n">
-        <v>67.15924219289856</v>
+        <v>61.53005294342042</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1035,36 +1196,65 @@
         <v>9</v>
       </c>
       <c r="V6" t="n">
-        <v>2.144739704252533e-05</v>
+        <v>8.357401231067872e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.07503159184029413</v>
+        <v>-0.08159665167577887</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2511534675913003</v>
+        <v>0.2111510325850313</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9819042850182381</v>
+        <v>0.9971890611385923</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2465068002468601</v>
+        <v>0.2090034446683001</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1149183807113324</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.4004157399759833</v>
+        <v>0.1497879482618544</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>flattest_linear_post_ir_window</t>
+        </is>
       </c>
       <c r="AC6" t="n">
-        <v>1.974415799951998</v>
+        <v>0.3329790938609002</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.574000059976015</v>
+        <v>0.01094439648849281</v>
       </c>
       <c r="AE6" t="n">
-        <v>1575</v>
+        <v>0.1169641801498956</v>
       </c>
       <c r="AF6" t="n">
+        <v>0.9481568649679805</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.01543914422891562</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.9971887853564337</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.1800021509961461</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.3638626182180189</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.011415569926982</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.741415560012996</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.7299999900860143</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>731</v>
+      </c>
+      <c r="AO6" t="n">
         <v>46.69696801056996</v>
       </c>
     </row>

--- a/data/processed/GCD/tables/hBN_GCD_fit_summary_refit_auxiliary.xlsx
+++ b/data/processed/GCD/tables/hBN_GCD_fit_summary_refit_auxiliary.xlsx
@@ -631,13 +631,13 @@
         <v>0.2537316398228566</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2177949015737403</v>
+        <v>0.2537241435900029</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1855998158946897</v>
+        <v>0.253450206173303</v>
       </c>
       <c r="E2" t="n">
-        <v>0.251491677559279</v>
+        <v>0.2539464962861953</v>
       </c>
       <c r="F2" t="n">
         <v>0.009867003129131019</v>
@@ -655,13 +655,13 @@
         <v>99.0876457235766</v>
       </c>
       <c r="K2" t="n">
-        <v>99.12647789014086</v>
+        <v>99.12647789014089</v>
       </c>
       <c r="L2" t="n">
-        <v>98.6000265889823</v>
+        <v>98.6000265889824</v>
       </c>
       <c r="M2" t="n">
-        <v>99.65238835783501</v>
+        <v>99.65238835783461</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -758,13 +758,13 @@
         <v>0.2618697187305725</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2272136017138796</v>
+        <v>0.2618737589822269</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1909342262815798</v>
+        <v>0.261842705609033</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2591578101708976</v>
+        <v>0.2619062476894733</v>
       </c>
       <c r="F3" t="n">
         <v>0.009732716467688456</v>
@@ -782,13 +782,13 @@
         <v>90.02908328210498</v>
       </c>
       <c r="K3" t="n">
-        <v>90.01799915214005</v>
+        <v>90.01799915214001</v>
       </c>
       <c r="L3" t="n">
-        <v>89.9074379826454</v>
+        <v>89.90743798264548</v>
       </c>
       <c r="M3" t="n">
-        <v>90.13615425000829</v>
+        <v>90.13615425000822</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -885,13 +885,13 @@
         <v>0.2704394929563628</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2334202096327406</v>
+        <v>0.2704421606048116</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2016192663000049</v>
+        <v>0.2703784413486048</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2684717613610291</v>
+        <v>0.2705005926383221</v>
       </c>
       <c r="F4" t="n">
         <v>0.009627444607500105</v>
@@ -909,13 +909,13 @@
         <v>82.62651540927513</v>
       </c>
       <c r="K4" t="n">
-        <v>82.61991512795704</v>
+        <v>82.61991512795697</v>
       </c>
       <c r="L4" t="n">
-        <v>82.5122170999024</v>
+        <v>82.51221709990232</v>
       </c>
       <c r="M4" t="n">
-        <v>82.72682779643704</v>
+        <v>82.72682779643702</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -1012,13 +1012,13 @@
         <v>0.2578444668184073</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2250812286125191</v>
+        <v>0.2578470906673032</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1969902141635942</v>
+        <v>0.2577469804650481</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2560473574389029</v>
+        <v>0.2579271298207772</v>
       </c>
       <c r="F5" t="n">
         <v>0.009465826381994863</v>
@@ -1036,13 +1036,13 @@
         <v>70.89006794626557</v>
       </c>
       <c r="K5" t="n">
-        <v>70.88641253948954</v>
+        <v>70.8864125394895</v>
       </c>
       <c r="L5" t="n">
-        <v>70.75556429483144</v>
+        <v>70.75556429483119</v>
       </c>
       <c r="M5" t="n">
-        <v>71.08057868838678</v>
+        <v>71.08057868838701</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1139,13 +1139,13 @@
         <v>0.2578480005956012</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2287151148614127</v>
+        <v>0.2578636798774953</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2019028414552028</v>
+        <v>0.2577174704048839</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2573337330206235</v>
+        <v>0.2580239002510678</v>
       </c>
       <c r="F6" t="n">
         <v>0.009339393602113992</v>
@@ -1163,13 +1163,13 @@
         <v>61.27702420765139</v>
       </c>
       <c r="K6" t="n">
-        <v>61.25395957124961</v>
+        <v>61.2539595712496</v>
       </c>
       <c r="L6" t="n">
-        <v>60.92660592733132</v>
+        <v>60.92660592733156</v>
       </c>
       <c r="M6" t="n">
-        <v>61.53005294342042</v>
+        <v>61.5300529434202</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
